--- a/AtchisonRegime/Outputs/USA/USA_Momentum/df_regEquityReturns_USA_Momentum.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA_Momentum/df_regEquityReturns_USA_Momentum.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q143"/>
+  <dimension ref="A1:Q144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7996,7 +7996,7 @@
         <v>-1.113652454430497</v>
       </c>
       <c r="C133" t="n">
-        <v>0.006266379198084816</v>
+        <v>-0.01570867082860625</v>
       </c>
       <c r="D133" t="b">
         <v>0</v>
@@ -8053,7 +8053,7 @@
         <v>-1.13653593688915</v>
       </c>
       <c r="C134" t="n">
-        <v>0.02240605369896704</v>
+        <v>0.005131485533573125</v>
       </c>
       <c r="D134" t="b">
         <v>0</v>
@@ -8110,7 +8110,7 @@
         <v>-1.151360964367</v>
       </c>
       <c r="C135" t="n">
-        <v>0.05890779434252914</v>
+        <v>0.04460226520446691</v>
       </c>
       <c r="D135" t="b">
         <v>0</v>
@@ -8167,7 +8167,7 @@
         <v>-1.199054339561413</v>
       </c>
       <c r="C136" t="n">
-        <v>0.1365357185829741</v>
+        <v>0.10691331821946</v>
       </c>
       <c r="D136" t="b">
         <v>0</v>
@@ -8224,7 +8224,7 @@
         <v>-1.211312601852137</v>
       </c>
       <c r="C137" t="n">
-        <v>0.19626538484902</v>
+        <v>0.1742576329953394</v>
       </c>
       <c r="D137" t="b">
         <v>0</v>
@@ -8281,7 +8281,7 @@
         <v>-1.189056899431358</v>
       </c>
       <c r="C138" t="n">
-        <v>0.2479141243562677</v>
+        <v>0.2230893786343014</v>
       </c>
       <c r="D138" t="b">
         <v>0</v>
@@ -8338,7 +8338,7 @@
         <v>-1.098247223033612</v>
       </c>
       <c r="C139" t="n">
-        <v>0.2597235153389927</v>
+        <v>0.2419933628466199</v>
       </c>
       <c r="D139" t="b">
         <v>0</v>
@@ -8395,7 +8395,7 @@
         <v>-0.9817076186491491</v>
       </c>
       <c r="C140" t="n">
-        <v>0.2098083315261438</v>
+        <v>0.2090047006632499</v>
       </c>
       <c r="D140" t="b">
         <v>0</v>
@@ -8452,7 +8452,7 @@
         <v>-0.8763018590939128</v>
       </c>
       <c r="C141" t="n">
-        <v>0.1536160686024298</v>
+        <v>0.1277646818410845</v>
       </c>
       <c r="D141" t="b">
         <v>0</v>
@@ -8506,10 +8506,10 @@
         <v>45716</v>
       </c>
       <c r="B142" t="n">
-        <v>-0.8167702922088305</v>
+        <v>-0.8165764810113098</v>
       </c>
       <c r="C142" t="n">
-        <v>0.04657800836005581</v>
+        <v>0.03018097094312175</v>
       </c>
       <c r="D142" t="b">
         <v>0</v>
@@ -8563,10 +8563,10 @@
         <v>45747</v>
       </c>
       <c r="B143" t="n">
-        <v>-0.7844280456827043</v>
+        <v>-0.836774216411349</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>-0.04969816765883398</v>
       </c>
       <c r="D143" t="b">
         <v>0</v>
@@ -8612,6 +8612,63 @@
         <v>154.025919125058</v>
       </c>
       <c r="Q143" t="n">
+        <v>103.9009996628157</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B144" t="n">
+        <v>-0.879407738343786</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-0.07980487945422567</v>
+      </c>
+      <c r="D144" t="b">
+        <v>0</v>
+      </c>
+      <c r="E144" t="b">
+        <v>1</v>
+      </c>
+      <c r="F144" t="n">
+        <v>-13.3055123347488</v>
+      </c>
+      <c r="G144" t="n">
+        <v>584630.9430503827</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>-13.3055123347488</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>220.3298353768061</v>
+      </c>
+      <c r="O144" t="n">
+        <v>159.898632180257</v>
+      </c>
+      <c r="P144" t="n">
+        <v>154.025919125058</v>
+      </c>
+      <c r="Q144" t="n">
         <v>103.9009996628157</v>
       </c>
     </row>
